--- a/GWD Data/Iron Structure.xlsx
+++ b/GWD Data/Iron Structure.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="67">
   <si>
-    <t>Estimate  For Fabricated Angle Iron Structure To Support 5000 Litres Capacity Water Tank At 4 m Height</t>
+    <t>Angle Iron Structure To Support 5000 Litres Capacity Water Tank At 4 m Height</t>
   </si>
   <si>
     <t>Quantity of angle iron, flats, M.S. sheets etc</t>
@@ -464,7 +464,7 @@
     <t>Say Rs. 71000 x Index</t>
   </si>
   <si>
-    <t>Estimate  For Fabricated Angle Iron Structure To Support 3000 Litres Capacity Water Tank At 4 m Height</t>
+    <t>Angle Iron Structure To Support 3000 Litres Capacity Water Tank At 4 m Height</t>
   </si>
   <si>
     <r>
@@ -533,7 +533,7 @@
     <t>Say Rs. 62000 x Index</t>
   </si>
   <si>
-    <t>Estimate  For Fabricated Angle Iron Structure To Support 5000 Litres Capacity Water Tank At 6 m Height</t>
+    <t>Angle Iron Structure To Support 5000 Litres Capacity Water Tank At 6 m Height</t>
   </si>
   <si>
     <r>
@@ -599,7 +599,7 @@
     <t>Say Rs. 94000 x Index</t>
   </si>
   <si>
-    <t>Estimate  For Fabricated Angle Iron Structure To Support 3000 Litres Capacity Water Tank At 6 m Height</t>
+    <t>Angle Iron Structure To Support 3000 Litres Capacity Water Tank At 6 m Height</t>
   </si>
   <si>
     <t>Say Rs.83000 x Index</t>
@@ -1423,7 +1423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68552385-706F-4098-AF41-61698754B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82E27A66-B913-4B3A-86E4-F790FE6AB9A6}">
   <dimension ref="A1:J176"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/Iron Structure.xlsx
+++ b/GWD Data/Iron Structure.xlsx
@@ -1423,7 +1423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82E27A66-B913-4B3A-86E4-F790FE6AB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A925931-AC5A-49BF-B22D-75D2CD98B9A6}">
   <dimension ref="A1:J176"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
